--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
   <si>
     <t>##</t>
   </si>
@@ -1174,6 +1174,9 @@
       <c r="J5">
         <v>2</v>
       </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -88,7 +88,7 @@
     <t>注释</t>
   </si>
   <si>
-    <t>demo.EQuestProgressType</t>
+    <t>demo.EQuestObjectiveType</t>
   </si>
   <si>
     <t>KillMonster</t>

--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>##</t>
   </si>
@@ -91,13 +91,19 @@
     <t>demo.EQuestObjectiveType</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0: </t>
+  </si>
+  <si>
     <t>KillMonster</t>
   </si>
   <si>
-    <t xml:space="preserve">P0: </t>
-  </si>
-  <si>
     <t>OwnItem</t>
+  </si>
+  <si>
+    <t>PlayerKilled</t>
   </si>
 </sst>
 </file>
@@ -1061,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col min="11" max="11" width="57.625" customWidth="1"/>
   </cols>
@@ -1161,7 +1167,7 @@
         <v>20</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -1172,10 +1178,26 @@
         <v>22</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -1,277 +1,179 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>demo.EQuestObjectiveType</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P0: </t>
-  </si>
-  <si>
-    <t>KillMonster</t>
-  </si>
-  <si>
-    <t>OwnItem</t>
-  </si>
-  <si>
-    <t>PlayerKilled</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -469,7 +371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -590,172 +492,219 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -809,11 +758,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1065,139 +1077,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="11" max="11" width="57.625" customWidth="1"/>
+    <col width="57.625" customWidth="1" style="5" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="6" t="n"/>
+      <c r="K1" s="6" t="n"/>
+      <c r="L1" s="7" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="175.5" customHeight="1" s="5">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>demo.EQuestObjectiveType</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0: </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>KillMonster</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P0: </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>OwnItem</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="7">
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>PlayerKilled</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SubmitItem</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="175.5" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>3</v>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>P0: obj_p4=item_id obj_p5=character_key</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1205,31 +1293,34 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="57.625" customWidth="1" style="5" min="11" max="11"/>
@@ -1274,17 +1274,143 @@
       </c>
     </row>
     <row r="8">
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>SubmitItem</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>P0: obj_p4=item_id obj_p5=character_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>demo.EQuestDialogRole</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>任务对话角色</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Hub 接取入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Hub 递交入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Hub 复述入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>AcceptSuccess</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>接取成功结果对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AcceptFail</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>接取失败结果对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>FulfillSuccess</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>递交成功结果对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>FulfillFail</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>递交失败结果对话</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="57.625" customWidth="1" style="5" min="11" max="11"/>
@@ -1289,126 +1289,141 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Talk</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>obj_p5=character_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>demo.EQuestDialogRole</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>任务对话角色</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="H10" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Accept</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Hub 接取入口</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="H11" t="inlineStr">
+    <row r="12">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Fulfill</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Hub 递交入口</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="H12" t="inlineStr">
+    <row r="13">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Remind</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Hub 复述入口</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="H13" t="inlineStr">
+    <row r="14">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>AcceptSuccess</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>接取成功结果对话</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="H14" t="inlineStr">
+    <row r="15">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>AcceptFail</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>接取失败结果对话</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="H15" t="inlineStr">
+    <row r="16">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>FulfillSuccess</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>递交成功结果对话</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="H16" t="inlineStr">
+    <row r="17">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>FulfillFail</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>递交失败结果对话</t>
         </is>

--- a/Config/Datas/quest_define.xlsx
+++ b/Config/Datas/quest_define.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="57.625" customWidth="1" style="5" min="11" max="11"/>
@@ -1289,141 +1289,156 @@
       </c>
     </row>
     <row r="9">
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Talk</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>obj_p5=character_key</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>InteractEntity</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>obj_p0=interact_id(0=any) obj_p4=cfg_id obj_p5=uniq_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>demo.EQuestDialogRole</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>任务对话角色</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>Hub 接取入口</t>
-        </is>
-      </c>
+      <c r="K11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Fulfill</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Hub 递交入口</t>
+          <t>Hub 接取入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Remind</t>
+          <t>Fulfill</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Hub 复述入口</t>
+          <t>Hub 递交入口</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>AcceptSuccess</t>
+          <t>Remind</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>接取成功结果对话</t>
+          <t>Hub 复述入口</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>AcceptFail</t>
+          <t>AcceptSuccess</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>接取失败结果对话</t>
+          <t>接取成功结果对话</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>FulfillSuccess</t>
+          <t>AcceptFail</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>递交成功结果对话</t>
+          <t>接取失败结果对话</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="H17" s="4" t="inlineStr">
         <is>
+          <t>FulfillSuccess</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>递交成功结果对话</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
           <t>FulfillFail</t>
         </is>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>递交失败结果对话</t>
         </is>
